--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/172.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/172.xlsx
@@ -426,13 +426,13 @@
         <v>-0.9859758249583616</v>
       </c>
       <c r="E2">
-        <v>-8.072930804077579</v>
+        <v>-7.325800519922085</v>
       </c>
       <c r="F2">
-        <v>-4.940338782271419</v>
+        <v>-3.937813345150363</v>
       </c>
       <c r="G2">
-        <v>-9.210961799492411</v>
+        <v>-9.492272096146442</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.015508708086535</v>
       </c>
       <c r="E3">
-        <v>-8.294282613572506</v>
+        <v>-8.141251891431301</v>
       </c>
       <c r="F3">
-        <v>-4.746092500625025</v>
+        <v>-4.264363210825526</v>
       </c>
       <c r="G3">
-        <v>-8.838055328857825</v>
+        <v>-8.60932642700404</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.9994765211083044</v>
       </c>
       <c r="E4">
-        <v>-9.075412680577589</v>
+        <v>-9.968350770832053</v>
       </c>
       <c r="F4">
-        <v>-5.075777312159801</v>
+        <v>-4.191188079002647</v>
       </c>
       <c r="G4">
-        <v>-9.033980034962973</v>
+        <v>-7.333581219081575</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.9098784207811189</v>
       </c>
       <c r="E5">
-        <v>-9.789856439345717</v>
+        <v>-7.435135996363278</v>
       </c>
       <c r="F5">
-        <v>-5.136947953143649</v>
+        <v>-4.011443000570973</v>
       </c>
       <c r="G5">
-        <v>-8.772533011544571</v>
+        <v>-7.138950936282282</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.7249321409781039</v>
       </c>
       <c r="E6">
-        <v>-11.10082702219625</v>
+        <v>-9.03797125748217</v>
       </c>
       <c r="F6">
-        <v>-4.905985033553707</v>
+        <v>-4.179684831085853</v>
       </c>
       <c r="G6">
-        <v>-7.328304209491976</v>
+        <v>-7.31170513415807</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.4274315850992574</v>
       </c>
       <c r="E7">
-        <v>-10.83614224492192</v>
+        <v>-10.77180168622094</v>
       </c>
       <c r="F7">
-        <v>-5.034974712954419</v>
+        <v>-3.900519446400637</v>
       </c>
       <c r="G7">
-        <v>-7.044967858967913</v>
+        <v>-7.111284707210593</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.005203100919540796</v>
       </c>
       <c r="E8">
-        <v>-11.91597045747294</v>
+        <v>-12.76634089205531</v>
       </c>
       <c r="F8">
-        <v>-4.944604494154655</v>
+        <v>-4.5527663521155</v>
       </c>
       <c r="G8">
-        <v>-7.205360479800062</v>
+        <v>-6.782385318429539</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.5394272362596565</v>
       </c>
       <c r="E9">
-        <v>-13.37837773961398</v>
+        <v>-12.13074692270873</v>
       </c>
       <c r="F9">
-        <v>-4.978764238897726</v>
+        <v>-4.666202455720682</v>
       </c>
       <c r="G9">
-        <v>-5.575939760280638</v>
+        <v>-5.831752235191201</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.195696875307803</v>
       </c>
       <c r="E10">
-        <v>-13.80976470205866</v>
+        <v>-12.21508522262759</v>
       </c>
       <c r="F10">
-        <v>-5.138312315789801</v>
+        <v>-4.730353631237388</v>
       </c>
       <c r="G10">
-        <v>-6.139546896159399</v>
+        <v>-6.16211819564615</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.936897437627415</v>
       </c>
       <c r="E11">
-        <v>-14.9294525428252</v>
+        <v>-13.29509910261292</v>
       </c>
       <c r="F11">
-        <v>-4.782822600068854</v>
+        <v>-4.292635528827952</v>
       </c>
       <c r="G11">
-        <v>-5.725265227375004</v>
+        <v>-5.537974424036276</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.719158567696531</v>
       </c>
       <c r="E12">
-        <v>-14.32899047483013</v>
+        <v>-13.56703396677353</v>
       </c>
       <c r="F12">
-        <v>-4.92265591387258</v>
+        <v>-4.568867890157773</v>
       </c>
       <c r="G12">
-        <v>-4.740123017435302</v>
+        <v>-5.069575267321413</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.491949362691959</v>
       </c>
       <c r="E13">
-        <v>-15.9106188921711</v>
+        <v>-14.6757629004415</v>
       </c>
       <c r="F13">
-        <v>-4.842111006572202</v>
+        <v>-4.013725120795122</v>
       </c>
       <c r="G13">
-        <v>-4.735637228229589</v>
+        <v>-4.654207739600135</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.194424416958829</v>
       </c>
       <c r="E14">
-        <v>-16.58374032561924</v>
+        <v>-16.5589197595832</v>
       </c>
       <c r="F14">
-        <v>-4.603144037285629</v>
+        <v>-4.154861032714297</v>
       </c>
       <c r="G14">
-        <v>-4.418016868100833</v>
+        <v>-4.553504254841045</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.770909190923045</v>
       </c>
       <c r="E15">
-        <v>-17.06326949523947</v>
+        <v>-16.48698042149735</v>
       </c>
       <c r="F15">
-        <v>-4.656947278350853</v>
+        <v>-4.127620499115781</v>
       </c>
       <c r="G15">
-        <v>-4.087697255283432</v>
+        <v>-3.266850799366681</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.183793025622514</v>
       </c>
       <c r="E16">
-        <v>-18.17585216028797</v>
+        <v>-16.90600012142709</v>
       </c>
       <c r="F16">
-        <v>-4.33485633668061</v>
+        <v>-3.607686679665179</v>
       </c>
       <c r="G16">
-        <v>-3.564554917531181</v>
+        <v>-3.74793596658803</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.414345107932194</v>
       </c>
       <c r="E17">
-        <v>-19.37451205927427</v>
+        <v>-17.95827256964143</v>
       </c>
       <c r="F17">
-        <v>-4.480125721039082</v>
+        <v>-3.969620494756049</v>
       </c>
       <c r="G17">
-        <v>-3.144456620234286</v>
+        <v>-2.824548673137893</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.467637593210902</v>
       </c>
       <c r="E18">
-        <v>-19.66456987641357</v>
+        <v>-17.47642482132927</v>
       </c>
       <c r="F18">
-        <v>-4.576631216555257</v>
+        <v>-3.843854448746214</v>
       </c>
       <c r="G18">
-        <v>-3.295728688105743</v>
+        <v>-2.690531168617117</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.364767650228855</v>
       </c>
       <c r="E19">
-        <v>-21.40209101146859</v>
+        <v>-19.43423810296143</v>
       </c>
       <c r="F19">
-        <v>-3.906717279500709</v>
+        <v>-3.539231783323267</v>
       </c>
       <c r="G19">
-        <v>-2.190215042358141</v>
+        <v>-2.631639874019021</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.134024362635341</v>
       </c>
       <c r="E20">
-        <v>-21.40545113918229</v>
+        <v>-19.5224210773128</v>
       </c>
       <c r="F20">
-        <v>-3.760683757038038</v>
+        <v>-3.208847765626824</v>
       </c>
       <c r="G20">
-        <v>-2.697711741891796</v>
+        <v>-2.883843854291779</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.80573155391347</v>
       </c>
       <c r="E21">
-        <v>-21.19965916637771</v>
+        <v>-19.14732304678345</v>
       </c>
       <c r="F21">
-        <v>-3.246636572475125</v>
+        <v>-3.177767537036325</v>
       </c>
       <c r="G21">
-        <v>-3.521921712076447</v>
+        <v>-3.586672672279052</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.407805157279277</v>
       </c>
       <c r="E22">
-        <v>-22.74995507205961</v>
+        <v>-21.57405981190988</v>
       </c>
       <c r="F22">
-        <v>-3.092696398229622</v>
+        <v>-2.274466026635297</v>
       </c>
       <c r="G22">
-        <v>-3.343877262428903</v>
+        <v>-3.418592964704715</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.965588750926442</v>
       </c>
       <c r="E23">
-        <v>-22.34317583737261</v>
+        <v>-20.64208627570929</v>
       </c>
       <c r="F23">
-        <v>-2.926531598022842</v>
+        <v>-2.496861097222712</v>
       </c>
       <c r="G23">
-        <v>-4.403761659008731</v>
+        <v>-3.759834067256171</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.500896627789106</v>
       </c>
       <c r="E24">
-        <v>-22.25967983361918</v>
+        <v>-20.93473890845499</v>
       </c>
       <c r="F24">
-        <v>-3.035903120396048</v>
+        <v>-2.382230879357289</v>
       </c>
       <c r="G24">
-        <v>-3.788188889800029</v>
+        <v>-3.252463168453008</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.036075317404208</v>
       </c>
       <c r="E25">
-        <v>-22.04141644339749</v>
+        <v>-23.78238827564635</v>
       </c>
       <c r="F25">
-        <v>-3.22542045617894</v>
+        <v>-2.18968074674633</v>
       </c>
       <c r="G25">
-        <v>-4.788652304495478</v>
+        <v>-4.503865935025213</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.58894659017432</v>
       </c>
       <c r="E26">
-        <v>-22.44622126341715</v>
+        <v>-22.46301284503759</v>
       </c>
       <c r="F26">
-        <v>-3.025944777599765</v>
+        <v>-1.967802756140306</v>
       </c>
       <c r="G26">
-        <v>-5.543089216894449</v>
+        <v>-4.520902002370303</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.174454274967522</v>
       </c>
       <c r="E27">
-        <v>-22.78444393010203</v>
+        <v>-22.79311595782672</v>
       </c>
       <c r="F27">
-        <v>-3.069982887990389</v>
+        <v>-2.087523004817951</v>
       </c>
       <c r="G27">
-        <v>-5.034453689695285</v>
+        <v>-5.340636114985859</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.808514924203505</v>
       </c>
       <c r="E28">
-        <v>-22.40299245053993</v>
+        <v>-21.49506511132007</v>
       </c>
       <c r="F28">
-        <v>-3.039234445789175</v>
+        <v>-2.073277570108573</v>
       </c>
       <c r="G28">
-        <v>-5.419066249356733</v>
+        <v>-5.98215362958583</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.502734681830332</v>
       </c>
       <c r="E29">
-        <v>-22.82128306615443</v>
+        <v>-21.41723422855024</v>
       </c>
       <c r="F29">
-        <v>-3.196105267831198</v>
+        <v>-1.998715903756726</v>
       </c>
       <c r="G29">
-        <v>-5.713681628533093</v>
+        <v>-5.379395982159646</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.268045594503941</v>
       </c>
       <c r="E30">
-        <v>-22.24445057553139</v>
+        <v>-20.79424753084102</v>
       </c>
       <c r="F30">
-        <v>-3.133780105234994</v>
+        <v>-1.849439743432193</v>
       </c>
       <c r="G30">
-        <v>-5.290968000260174</v>
+        <v>-5.612458388124337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.111743473209462</v>
       </c>
       <c r="E31">
-        <v>-22.27322449937612</v>
+        <v>-20.02355106794962</v>
       </c>
       <c r="F31">
-        <v>-2.885485108106483</v>
+        <v>-2.16191363093093</v>
       </c>
       <c r="G31">
-        <v>-5.351054401797946</v>
+        <v>-5.526847680478784</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.035597498572203</v>
       </c>
       <c r="E32">
-        <v>-20.71412524022331</v>
+        <v>-20.23820073591319</v>
       </c>
       <c r="F32">
-        <v>-3.105356543317645</v>
+        <v>-2.003139986231506</v>
       </c>
       <c r="G32">
-        <v>-5.566849002229798</v>
+        <v>-5.503140863872064</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.040399455496512</v>
       </c>
       <c r="E33">
-        <v>-20.64436862660916</v>
+        <v>-20.90192558579541</v>
       </c>
       <c r="F33">
-        <v>-3.051014050388213</v>
+        <v>-2.289534988420703</v>
       </c>
       <c r="G33">
-        <v>-4.850208588252686</v>
+        <v>-4.77514858924079</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.119175257602069</v>
       </c>
       <c r="E34">
-        <v>-21.06427137897039</v>
+        <v>-19.22293950576353</v>
       </c>
       <c r="F34">
-        <v>-3.040314533223504</v>
+        <v>-2.172495953857897</v>
       </c>
       <c r="G34">
-        <v>-5.291457960999986</v>
+        <v>-5.490875292649064</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.261089980253531</v>
       </c>
       <c r="E35">
-        <v>-19.69817115355048</v>
+        <v>-20.24875208035106</v>
       </c>
       <c r="F35">
-        <v>-2.860091967458327</v>
+        <v>-2.117463757002291</v>
       </c>
       <c r="G35">
-        <v>-4.445630128443893</v>
+        <v>-4.991899937333493</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.45226923211063</v>
       </c>
       <c r="E36">
-        <v>-19.14589204899703</v>
+        <v>-18.98592823315008</v>
       </c>
       <c r="F36">
-        <v>-3.068046807508765</v>
+        <v>-1.641759676358083</v>
       </c>
       <c r="G36">
-        <v>-3.627640673327533</v>
+        <v>-4.117402780407312</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.675706013742727</v>
       </c>
       <c r="E37">
-        <v>-18.62077926001559</v>
+        <v>-18.21658578398696</v>
       </c>
       <c r="F37">
-        <v>-3.210062468063966</v>
+        <v>-1.877214777777169</v>
       </c>
       <c r="G37">
-        <v>-3.568044232529573</v>
+        <v>-4.155712413387759</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.916480683935824</v>
       </c>
       <c r="E38">
-        <v>-18.3812048711138</v>
+        <v>-18.06308862902297</v>
       </c>
       <c r="F38">
-        <v>-2.754829370082728</v>
+        <v>-2.026225667360867</v>
       </c>
       <c r="G38">
-        <v>-3.159460012618263</v>
+        <v>-4.606996049664589</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.159868698161529</v>
       </c>
       <c r="E39">
-        <v>-18.04827599054388</v>
+        <v>-18.02421167966712</v>
       </c>
       <c r="F39">
-        <v>-3.100548412158371</v>
+        <v>-1.645166227782193</v>
       </c>
       <c r="G39">
-        <v>-3.604211942546111</v>
+        <v>-3.684750894425501</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.393936625260909</v>
       </c>
       <c r="E40">
-        <v>-17.93306708331474</v>
+        <v>-16.85734619668868</v>
       </c>
       <c r="F40">
-        <v>-3.047167228719611</v>
+        <v>-1.804295414459633</v>
       </c>
       <c r="G40">
-        <v>-3.762283870955232</v>
+        <v>-4.070601598118635</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.610383160849916</v>
       </c>
       <c r="E41">
-        <v>-17.51959023557039</v>
+        <v>-16.72741069198659</v>
       </c>
       <c r="F41">
-        <v>-3.020739928108673</v>
+        <v>-2.040102890444905</v>
       </c>
       <c r="G41">
-        <v>-3.97841614703209</v>
+        <v>-3.931899671659791</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.802218053860548</v>
       </c>
       <c r="E42">
-        <v>-17.35065551271425</v>
+        <v>-17.12000674608157</v>
       </c>
       <c r="F42">
-        <v>-2.908734702798091</v>
+        <v>-2.11588084293981</v>
       </c>
       <c r="G42">
-        <v>-3.474186955945696</v>
+        <v>-4.114568953425696</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.967294967091683</v>
       </c>
       <c r="E43">
-        <v>-16.63291502486853</v>
+        <v>-14.8788559027375</v>
       </c>
       <c r="F43">
-        <v>-2.875887850258919</v>
+        <v>-2.119091806683363</v>
       </c>
       <c r="G43">
-        <v>-3.34125862090734</v>
+        <v>-4.586493841139883</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.104443312237594</v>
       </c>
       <c r="E44">
-        <v>-16.21622296057874</v>
+        <v>-15.26355882663711</v>
       </c>
       <c r="F44">
-        <v>-2.769872992573487</v>
+        <v>-2.303738454923322</v>
       </c>
       <c r="G44">
-        <v>-3.13961991320141</v>
+        <v>-4.327794570519075</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.212814330893226</v>
       </c>
       <c r="E45">
-        <v>-14.76670824393754</v>
+        <v>-13.90131686107174</v>
       </c>
       <c r="F45">
-        <v>-3.214701142690288</v>
+        <v>-2.291318241281488</v>
       </c>
       <c r="G45">
-        <v>-3.877768941547167</v>
+        <v>-4.040180995158273</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.292433626599377</v>
       </c>
       <c r="E46">
-        <v>-15.11983864705567</v>
+        <v>-14.42419711236739</v>
       </c>
       <c r="F46">
-        <v>-3.503896136937982</v>
+        <v>-2.093433395294371</v>
       </c>
       <c r="G46">
-        <v>-4.442932033829387</v>
+        <v>-3.605549402943976</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.341018090460847</v>
       </c>
       <c r="E47">
-        <v>-14.39280120207222</v>
+        <v>-13.92504153639792</v>
       </c>
       <c r="F47">
-        <v>-3.217265954420343</v>
+        <v>-2.324625160389095</v>
       </c>
       <c r="G47">
-        <v>-4.778174427863684</v>
+        <v>-4.269035697742551</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.354480336463761</v>
       </c>
       <c r="E48">
-        <v>-12.93983125976317</v>
+        <v>-13.14135741005251</v>
       </c>
       <c r="F48">
-        <v>-3.063838109038485</v>
+        <v>-2.496818337162995</v>
       </c>
       <c r="G48">
-        <v>-4.454975798501256</v>
+        <v>-4.966978150513859</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.327320081912092</v>
       </c>
       <c r="E49">
-        <v>-13.3401936467813</v>
+        <v>-11.36202034601066</v>
       </c>
       <c r="F49">
-        <v>-3.353375183763913</v>
+        <v>-2.533920607496952</v>
       </c>
       <c r="G49">
-        <v>-4.456720456000452</v>
+        <v>-5.276927976628124</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.254097285165571</v>
       </c>
       <c r="E50">
-        <v>-12.5129456004821</v>
+        <v>-11.32158107312216</v>
       </c>
       <c r="F50">
-        <v>-3.392375525637525</v>
+        <v>-2.599949266376412</v>
       </c>
       <c r="G50">
-        <v>-5.1920952471843</v>
+        <v>-5.741897408164302</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.129363496377565</v>
       </c>
       <c r="E51">
-        <v>-12.20864120411467</v>
+        <v>-11.95351150699653</v>
       </c>
       <c r="F51">
-        <v>-3.415123085553939</v>
+        <v>-2.990561620037016</v>
       </c>
       <c r="G51">
-        <v>-4.410697251913504</v>
+        <v>-5.389066085679858</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.950406561061512</v>
       </c>
       <c r="E52">
-        <v>-12.54430528298522</v>
+        <v>-12.79628769066803</v>
       </c>
       <c r="F52">
-        <v>-3.51988127259547</v>
+        <v>-2.181927714437296</v>
       </c>
       <c r="G52">
-        <v>-5.239833313860591</v>
+        <v>-5.592836784713077</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.717618981432133</v>
       </c>
       <c r="E53">
-        <v>-12.20172622430496</v>
+        <v>-9.90426833514951</v>
       </c>
       <c r="F53">
-        <v>-3.850407031971344</v>
+        <v>-2.172909301101826</v>
       </c>
       <c r="G53">
-        <v>-5.651608899671759</v>
+        <v>-4.843716608450175</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.431709604657766</v>
       </c>
       <c r="E54">
-        <v>-10.68499989644192</v>
+        <v>-11.22292373839106</v>
       </c>
       <c r="F54">
-        <v>-3.572506236459607</v>
+        <v>-2.686549473244471</v>
       </c>
       <c r="G54">
-        <v>-5.391449678468132</v>
+        <v>-5.416838252208803</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.100069112470186</v>
       </c>
       <c r="E55">
-        <v>-11.15592043697357</v>
+        <v>-10.72884005331017</v>
       </c>
       <c r="F55">
-        <v>-3.610512011018323</v>
+        <v>-2.965375153010825</v>
       </c>
       <c r="G55">
-        <v>-6.06477822515496</v>
+        <v>-5.746171322455501</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.731666277576001</v>
       </c>
       <c r="E56">
-        <v>-10.55569837810091</v>
+        <v>-10.44722784019518</v>
       </c>
       <c r="F56">
-        <v>-3.62955686650444</v>
+        <v>-2.68705705099037</v>
       </c>
       <c r="G56">
-        <v>-5.696370785908244</v>
+        <v>-5.154974100052453</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.336643852249125</v>
       </c>
       <c r="E57">
-        <v>-9.999434216420703</v>
+        <v>-10.71199865847565</v>
       </c>
       <c r="F57">
-        <v>-3.373728180336183</v>
+        <v>-2.884481038556094</v>
       </c>
       <c r="G57">
-        <v>-6.290050917465746</v>
+        <v>-5.872068058768445</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.9304041678679649</v>
       </c>
       <c r="E58">
-        <v>-10.44212877846254</v>
+        <v>-9.70588041734748</v>
       </c>
       <c r="F58">
-        <v>-3.879056271981644</v>
+        <v>-2.929540639262177</v>
       </c>
       <c r="G58">
-        <v>-6.832252065887581</v>
+        <v>-6.612802623180373</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.5260857753065665</v>
       </c>
       <c r="E59">
-        <v>-9.760783636216475</v>
+        <v>-8.905825857464341</v>
       </c>
       <c r="F59">
-        <v>-3.759142019329357</v>
+        <v>-2.834289438831029</v>
       </c>
       <c r="G59">
-        <v>-5.31691936674252</v>
+        <v>-5.591899900325464</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.1368425691151126</v>
       </c>
       <c r="E60">
-        <v>-10.01156599828725</v>
+        <v>-8.031454510641327</v>
       </c>
       <c r="F60">
-        <v>-4.029488537624449</v>
+        <v>-3.085459654049021</v>
       </c>
       <c r="G60">
-        <v>-6.251757837212996</v>
+        <v>-6.330231008675881</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.2234008913672629</v>
       </c>
       <c r="E61">
-        <v>-9.118460354494504</v>
+        <v>-8.352265194766717</v>
       </c>
       <c r="F61">
-        <v>-3.814395935013124</v>
+        <v>-2.795350069635162</v>
       </c>
       <c r="G61">
-        <v>-5.926708612894116</v>
+        <v>-6.177830044775532</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.5455531479054727</v>
       </c>
       <c r="E62">
-        <v>-9.8649430668669</v>
+        <v>-9.30948950203407</v>
       </c>
       <c r="F62">
-        <v>-3.767118354172468</v>
+        <v>-2.92051430739713</v>
       </c>
       <c r="G62">
-        <v>-6.332022013812627</v>
+        <v>-5.823955900446217</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.8193289065823474</v>
       </c>
       <c r="E63">
-        <v>-8.997233105309167</v>
+        <v>-7.879691761222269</v>
       </c>
       <c r="F63">
-        <v>-3.809965517714683</v>
+        <v>-3.162342241419945</v>
       </c>
       <c r="G63">
-        <v>-6.121974520436948</v>
+        <v>-6.1533551816037</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.037270296098115</v>
       </c>
       <c r="E64">
-        <v>-9.062692197090042</v>
+        <v>-7.74972455720213</v>
       </c>
       <c r="F64">
-        <v>-3.663959710105531</v>
+        <v>-3.057725004204888</v>
       </c>
       <c r="G64">
-        <v>-6.7287842756032</v>
+        <v>-5.07944400357398</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.19607397474003</v>
       </c>
       <c r="E65">
-        <v>-8.67101089474461</v>
+        <v>-7.479415415210279</v>
       </c>
       <c r="F65">
-        <v>-3.56550467260745</v>
+        <v>-3.259472508919762</v>
       </c>
       <c r="G65">
-        <v>-5.7389046749968</v>
+        <v>-6.233361135651267</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.292220148496145</v>
       </c>
       <c r="E66">
-        <v>-9.816945770859602</v>
+        <v>-8.563695117710839</v>
       </c>
       <c r="F66">
-        <v>-3.852225126362269</v>
+        <v>-3.238664196896803</v>
       </c>
       <c r="G66">
-        <v>-6.139599864888028</v>
+        <v>-6.907090258348346</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.326793449230203</v>
       </c>
       <c r="E67">
-        <v>-8.600067820940447</v>
+        <v>-6.865621519736631</v>
       </c>
       <c r="F67">
-        <v>-3.846511115419363</v>
+        <v>-3.010220953418324</v>
       </c>
       <c r="G67">
-        <v>-6.388225145432833</v>
+        <v>-6.596302864212645</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.303463167328774</v>
       </c>
       <c r="E68">
-        <v>-8.336383836421817</v>
+        <v>-7.11286261513341</v>
       </c>
       <c r="F68">
-        <v>-3.885421186055795</v>
+        <v>-3.268431533283402</v>
       </c>
       <c r="G68">
-        <v>-6.440988620237738</v>
+        <v>-6.11052334341661</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.227553532601339</v>
       </c>
       <c r="E69">
-        <v>-8.653626083029165</v>
+        <v>-8.106047534495673</v>
       </c>
       <c r="F69">
-        <v>-3.790095551446622</v>
+        <v>-3.54665857221372</v>
       </c>
       <c r="G69">
-        <v>-6.715482503626408</v>
+        <v>-6.299101948970113</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.106903989840671</v>
       </c>
       <c r="E70">
-        <v>-8.152930825897084</v>
+        <v>-6.622546620426909</v>
       </c>
       <c r="F70">
-        <v>-4.007038714420137</v>
+        <v>-3.051040181535818</v>
       </c>
       <c r="G70">
-        <v>-7.056571321083058</v>
+        <v>-5.531310295865723</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.9501521638667635</v>
       </c>
       <c r="E71">
-        <v>-9.022098956085285</v>
+        <v>-8.588366244104627</v>
       </c>
       <c r="F71">
-        <v>-3.902068310785937</v>
+        <v>-3.232900299217561</v>
       </c>
       <c r="G71">
-        <v>-7.349630743855961</v>
+        <v>-6.850622283084998</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.7676111490143821</v>
       </c>
       <c r="E72">
-        <v>-9.593153113874541</v>
+        <v>-7.561213241210829</v>
       </c>
       <c r="F72">
-        <v>-3.602119161519452</v>
+        <v>-3.329055003873467</v>
       </c>
       <c r="G72">
-        <v>-6.791913068491562</v>
+        <v>-6.210131037602201</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.5697899729417467</v>
       </c>
       <c r="E73">
-        <v>-8.07858686811316</v>
+        <v>-8.183113105158206</v>
       </c>
       <c r="F73">
-        <v>-3.742382451479219</v>
+        <v>-2.737914599052877</v>
       </c>
       <c r="G73">
-        <v>-6.74713131898184</v>
+        <v>-6.004923561804937</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.3683579300376205</v>
       </c>
       <c r="E74">
-        <v>-8.68388081787441</v>
+        <v>-8.845696779590495</v>
       </c>
       <c r="F74">
-        <v>-3.682173119986043</v>
+        <v>-3.128370165827853</v>
       </c>
       <c r="G74">
-        <v>-6.588516461104279</v>
+        <v>-6.768769044626517</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.1751969106433707</v>
       </c>
       <c r="E75">
-        <v>-9.331950733112114</v>
+        <v>-8.502538076237251</v>
       </c>
       <c r="F75">
-        <v>-3.720210568663068</v>
+        <v>-3.209667333438064</v>
       </c>
       <c r="G75">
-        <v>-6.0964866303301</v>
+        <v>-5.741427310697725</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.001125345244000104</v>
       </c>
       <c r="E76">
-        <v>-10.14479823206692</v>
+        <v>-9.535261102160483</v>
       </c>
       <c r="F76">
-        <v>-4.124965416148546</v>
+        <v>-3.262437998246422</v>
       </c>
       <c r="G76">
-        <v>-6.52732764790193</v>
+        <v>-7.073587525154911</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.1432946139877875</v>
       </c>
       <c r="E77">
-        <v>-10.48550703098202</v>
+        <v>-10.86854800492081</v>
       </c>
       <c r="F77">
-        <v>-3.856961198902391</v>
+        <v>-3.210859072139432</v>
       </c>
       <c r="G77">
-        <v>-7.113602089088083</v>
+        <v>-6.07667963636864</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.250008591750741</v>
       </c>
       <c r="E78">
-        <v>-10.72843249064948</v>
+        <v>-10.65209600430219</v>
       </c>
       <c r="F78">
-        <v>-3.888623439416814</v>
+        <v>-2.989203592214527</v>
       </c>
       <c r="G78">
-        <v>-6.71865400625303</v>
+        <v>-6.089954923981117</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.3122430214736584</v>
       </c>
       <c r="E79">
-        <v>-11.03419505564739</v>
+        <v>-8.490854613297461</v>
       </c>
       <c r="F79">
-        <v>-3.94128007739926</v>
+        <v>-3.208216658819522</v>
       </c>
       <c r="G79">
-        <v>-7.213514353463287</v>
+        <v>-5.496291345151311</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.3254090023736613</v>
       </c>
       <c r="E80">
-        <v>-11.43992821283862</v>
+        <v>-10.33314199451994</v>
       </c>
       <c r="F80">
-        <v>-4.053536320097439</v>
+        <v>-3.20395965731882</v>
       </c>
       <c r="G80">
-        <v>-7.227865568376028</v>
+        <v>-5.920905226563773</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.2855835643782658</v>
       </c>
       <c r="E81">
-        <v>-12.13500368827594</v>
+        <v>-11.3299270507183</v>
       </c>
       <c r="F81">
-        <v>-4.19529858770617</v>
+        <v>-3.243489748821147</v>
       </c>
       <c r="G81">
-        <v>-6.841293165755331</v>
+        <v>-6.376929564052841</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.188879798230641</v>
       </c>
       <c r="E82">
-        <v>-12.85309286862025</v>
+        <v>-12.43287312307848</v>
       </c>
       <c r="F82">
-        <v>-4.267390464682889</v>
+        <v>-3.579691510197956</v>
       </c>
       <c r="G82">
-        <v>-6.091686339298156</v>
+        <v>-5.687756746415061</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.03385995357837969</v>
       </c>
       <c r="E83">
-        <v>-13.52873213361665</v>
+        <v>-12.9460488545757</v>
       </c>
       <c r="F83">
-        <v>-4.147852342185519</v>
+        <v>-4.182673284148287</v>
       </c>
       <c r="G83">
-        <v>-7.218503345590968</v>
+        <v>-6.016712414470281</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.1831265757517198</v>
       </c>
       <c r="E84">
-        <v>-14.90192847780658</v>
+        <v>-13.54778342376692</v>
       </c>
       <c r="F84">
-        <v>-3.718762269603398</v>
+        <v>-3.612037911667849</v>
       </c>
       <c r="G84">
-        <v>-6.607810320507152</v>
+        <v>-6.524242219459329</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4621701870125264</v>
       </c>
       <c r="E85">
-        <v>-16.24330776361861</v>
+        <v>-14.57678404405585</v>
       </c>
       <c r="F85">
-        <v>-3.886867901409549</v>
+        <v>-3.588682208679906</v>
       </c>
       <c r="G85">
-        <v>-6.571278450481294</v>
+        <v>-6.367908327458326</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8003915439830572</v>
       </c>
       <c r="E86">
-        <v>-16.65759520821034</v>
+        <v>-15.2889409234501</v>
       </c>
       <c r="F86">
-        <v>-4.161081037697185</v>
+        <v>-3.785343641847346</v>
       </c>
       <c r="G86">
-        <v>-6.468909761315951</v>
+        <v>-5.29575173856442</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.196793549761908</v>
       </c>
       <c r="E87">
-        <v>-17.55433268815723</v>
+        <v>-16.9009282305385</v>
       </c>
       <c r="F87">
-        <v>-4.572193672580196</v>
+        <v>-3.947241146464974</v>
       </c>
       <c r="G87">
-        <v>-6.552613594730883</v>
+        <v>-5.753530665189301</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.643798981690374</v>
       </c>
       <c r="E88">
-        <v>-20.21871471225818</v>
+        <v>-19.18442030585429</v>
       </c>
       <c r="F88">
-        <v>-4.346295444507828</v>
+        <v>-3.708842727602043</v>
       </c>
       <c r="G88">
-        <v>-6.807671265258493</v>
+        <v>-4.864606150802977</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.133445030583107</v>
       </c>
       <c r="E89">
-        <v>-21.23175246167007</v>
+        <v>-19.7642461177964</v>
       </c>
       <c r="F89">
-        <v>-4.226888769601441</v>
+        <v>-4.060447612712417</v>
       </c>
       <c r="G89">
-        <v>-6.63094110219004</v>
+        <v>-6.168812118726557</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.655701664774915</v>
       </c>
       <c r="E90">
-        <v>-22.22623705307254</v>
+        <v>-21.06778547480035</v>
       </c>
       <c r="F90">
-        <v>-4.111442151336609</v>
+        <v>-3.790413084482667</v>
       </c>
       <c r="G90">
-        <v>-6.705213191363589</v>
+        <v>-6.226240152196294</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.193985602744973</v>
       </c>
       <c r="E91">
-        <v>-23.15367305831743</v>
+        <v>-24.12202835469564</v>
       </c>
       <c r="F91">
-        <v>-4.098303727062123</v>
+        <v>-3.857908255039823</v>
       </c>
       <c r="G91">
-        <v>-7.052939652626478</v>
+        <v>-4.718760067070384</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.734508179517407</v>
       </c>
       <c r="E92">
-        <v>-25.85279300653122</v>
+        <v>-24.04460956306051</v>
       </c>
       <c r="F92">
-        <v>-4.216696038329673</v>
+        <v>-3.634240676749352</v>
       </c>
       <c r="G92">
-        <v>-6.802013542931879</v>
+        <v>-5.473759772211032</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.259267487656675</v>
       </c>
       <c r="E93">
-        <v>-27.88807036453859</v>
+        <v>-26.35361958940952</v>
       </c>
       <c r="F93">
-        <v>-4.244911342919141</v>
+        <v>-3.525391777328241</v>
       </c>
       <c r="G93">
-        <v>-7.665880538131459</v>
+        <v>-5.616566775138573</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.746249775082159</v>
       </c>
       <c r="E94">
-        <v>-30.26337498612289</v>
+        <v>-29.32173542215294</v>
       </c>
       <c r="F94">
-        <v>-4.15797143113222</v>
+        <v>-4.002118140140866</v>
       </c>
       <c r="G94">
-        <v>-7.538272249774712</v>
+        <v>-6.213593868236278</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.180358482373367</v>
       </c>
       <c r="E95">
-        <v>-32.39754742374677</v>
+        <v>-31.07913202962763</v>
       </c>
       <c r="F95">
-        <v>-3.856552602776207</v>
+        <v>-3.812185081555171</v>
       </c>
       <c r="G95">
-        <v>-7.882655060042937</v>
+        <v>-7.317028491385218</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.539552029070699</v>
       </c>
       <c r="E96">
-        <v>-35.05761607635541</v>
+        <v>-34.55759556185047</v>
       </c>
       <c r="F96">
-        <v>-3.784989683575245</v>
+        <v>-3.984748845513284</v>
       </c>
       <c r="G96">
-        <v>-7.556884136796494</v>
+        <v>-7.168497555220277</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.811949385110101</v>
       </c>
       <c r="E97">
-        <v>-36.68162421769716</v>
+        <v>-36.02752011084424</v>
       </c>
       <c r="F97">
-        <v>-3.911944300874617</v>
+        <v>-3.573610871335626</v>
       </c>
       <c r="G97">
-        <v>-7.580183756301885</v>
+        <v>-8.021933021425614</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.98173599901597</v>
       </c>
       <c r="E98">
-        <v>-40.17529889411177</v>
+        <v>-37.90770629103691</v>
       </c>
       <c r="F98">
-        <v>-3.678457745908422</v>
+        <v>-3.814986657319583</v>
       </c>
       <c r="G98">
-        <v>-8.351487898223443</v>
+        <v>-7.746353279100063</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.05463130732517</v>
       </c>
       <c r="E99">
-        <v>-40.87594892105253</v>
+        <v>-40.65561375397233</v>
       </c>
       <c r="F99">
-        <v>-3.579010516654317</v>
+        <v>-3.987946347756556</v>
       </c>
       <c r="G99">
-        <v>-8.860351853064817</v>
+        <v>-7.673163738317855</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.015756264463984</v>
       </c>
       <c r="E100">
-        <v>-44.64362571001225</v>
+        <v>-42.5078750991967</v>
       </c>
       <c r="F100">
-        <v>-3.692514719613862</v>
+        <v>-3.458236311689947</v>
       </c>
       <c r="G100">
-        <v>-9.184722415548148</v>
+        <v>-7.936772547973402</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.903371303314639</v>
       </c>
       <c r="E101">
-        <v>-46.8096650192281</v>
+        <v>-45.67328069479529</v>
       </c>
       <c r="F101">
-        <v>-3.726489962617785</v>
+        <v>-3.905358459825262</v>
       </c>
       <c r="G101">
-        <v>-10.01159737489191</v>
+        <v>-8.61286871073106</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.681181571411044</v>
       </c>
       <c r="E102">
-        <v>-49.7486661604577</v>
+        <v>-47.67602096705754</v>
       </c>
       <c r="F102">
-        <v>-3.804496189335712</v>
+        <v>-4.051544809908774</v>
       </c>
       <c r="G102">
-        <v>-9.555629316677013</v>
+        <v>-8.877848086239865</v>
       </c>
     </row>
   </sheetData>
